--- a/tests/fixtures/18_billing_statement/pattern.xlsx
+++ b/tests/fixtures/18_billing_statement/pattern.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I29"/>
+  <dimension ref="A1:I88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,7 +441,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>l_stmt</t>
+          <t>company_name_label</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -451,7 +451,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Statement #:</t>
+          <t>Your Company Name</t>
         </is>
       </c>
     </row>
@@ -463,7 +463,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>l_date</t>
+          <t>street_address_label</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -473,7 +473,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Date:</t>
+          <t>Street Address</t>
         </is>
       </c>
     </row>
@@ -485,7 +485,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>l_cust</t>
+          <t>phone_label</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -495,7 +495,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Customer:</t>
+          <t>Phone:</t>
         </is>
       </c>
     </row>
@@ -507,7 +507,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>c_date</t>
+          <t>phone_number_label</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -517,7 +517,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Date</t>
+          <t>(413) 555-0190</t>
         </is>
       </c>
     </row>
@@ -529,7 +529,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>c_type</t>
+          <t>fax_label</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -539,7 +539,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Type</t>
+          <t>Fax:</t>
         </is>
       </c>
     </row>
@@ -551,7 +551,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>c_inv</t>
+          <t>fax_number_label</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -561,7 +561,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Invoice #</t>
+          <t>(413) 555-0191</t>
         </is>
       </c>
     </row>
@@ -573,7 +573,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>c_desc</t>
+          <t>city_state_zip_label</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -583,7 +583,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>City, ST  ZIP Code</t>
         </is>
       </c>
     </row>
@@ -595,7 +595,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>c_amt</t>
+          <t>email_label</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -605,7 +605,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Amount</t>
+          <t>E-mail:</t>
         </is>
       </c>
     </row>
@@ -617,7 +617,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>c_pay</t>
+          <t>email_value_label</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -627,7 +627,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Payment</t>
+          <t>someone@example.com</t>
         </is>
       </c>
     </row>
@@ -639,7 +639,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>c_bal</t>
+          <t>statement_label</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -649,19 +649,19 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Balance</t>
+          <t>Statement</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>var:</t>
+          <t>lbl:</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>statement.number</t>
+          <t>statement_number_label</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -671,37 +671,41 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>ST-\d+</t>
+          <t>Statement #:</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>var:</t>
+          <t>lbl:</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>statement.date</t>
+          <t>bill_to_label</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Bill To:</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>var:</t>
+          <t>lbl:</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>statement.customer</t>
+          <t>date_label</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -711,37 +715,41 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>.+</t>
+          <t>Date:</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>var:</t>
+          <t>lbl:</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>txn.date</t>
+          <t>company_name_2_label</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Company Name</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>var:</t>
+          <t>lbl:</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>txn.type</t>
+          <t>customer_id_label</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -751,41 +759,41 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>.+</t>
+          <t>Customer ID:</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>var:</t>
+          <t>lbl:</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>txn.invoice</t>
+          <t>street_address_2_label</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>string</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>\d+</t>
+          <t>Street Address</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>var:</t>
+          <t>lbl:</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>txn.description</t>
+          <t>address_2_label</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -795,29 +803,29 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>.+</t>
+          <t>Address 2</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>var:</t>
+          <t>lbl:</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>txn.amount</t>
+          <t>city_state_zip_2_label</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>currency</t>
+          <t>string</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>.*</t>
+          <t>City, ST  ZIP Code</t>
         </is>
       </c>
     </row>
@@ -829,12 +837,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>txn.payment</t>
+          <t>contact.phone</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>currency</t>
+          <t>string</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -851,12 +859,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>txn.balance</t>
+          <t>contact.fax</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>currency</t>
+          <t>string</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -868,139 +876,1067 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>START:</t>
+          <t>var:</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>contact.email</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>.*</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>cell:C7</t>
+          <t>var:</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
           <t>statement.number</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>.*</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>cell:C8</t>
+          <t>var:</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>statement.date</t>
+          <t>statement.bill_to</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>.*</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>cell:C9</t>
+          <t>var:</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>statement.customer</t>
+          <t>statement.date</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>date</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>table:*</t>
+          <t>var:</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>statement.customer_id</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>.*</t>
         </is>
       </c>
     </row>
     <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>lbl:</t>
+        </is>
+      </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>HEADER:1</t>
+          <t>col_date</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>c_date</t>
+          <t>string</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>c_type</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>c_inv</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>c_desc</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>c_amt</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>c_pay</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>c_bal</t>
+          <t>Date</t>
         </is>
       </c>
     </row>
     <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>lbl:</t>
+        </is>
+      </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>DATA:*</t>
+          <t>col_type</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>txn.date</t>
+          <t>string</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>txn.type</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>txn.invoice</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>txn.description</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>txn.amount</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>txn.payment</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>txn.balance</t>
+          <t>Type</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
+        <is>
+          <t>lbl:</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>col_invoice</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Invoice #</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>lbl:</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>col_description</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>lbl:</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>col_amount</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Amount</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>lbl:</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>col_payment</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Payment</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>lbl:</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>col_balance</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Balance</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>var:</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>line.date</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>var:</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>line.type</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>.*</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>var:</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>line.invoice</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>\d+</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>var:</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>line.description</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>.*</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>var:</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>line.amount</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>currency</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>\d+(\.\d{1,2})?</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>var:</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>line.payment</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>currency</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>\d+(\.\d{1,2})?</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>var:</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>line.balance</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>currency</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>\d+(\.\d{1,2})?</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>lbl:</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>col_customer_name</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Customer Name:</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>lbl:</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>col_customer_value</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Enter customer name</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>var:</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>remittance.customer_name</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>.*</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>var:</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>remittance.value</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>START:</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>cell:next</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>company_name_label</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>cell:next</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>IGNORE</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>cell:next</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>street_address_label</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>cell:next</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>contact.phone</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>cell:next</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>phone_label</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>cell:next</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>IGNORE</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>cell:next</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>fax_label</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>cell:next</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>contact.fax</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>cell:next</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>phone_number_label</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>cell:next</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>IGNORE</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>cell:next</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>fax_number_label</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>cell:next</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>IGNORE</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>cell:next</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>city_state_zip_label</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>cell:next</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>contact.email</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>cell:next</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>email_label</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>cell:next</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>IGNORE</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>cell:next</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>email_value_label</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>cell:next</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>IGNORE</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>cell:next</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>statement_label</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>cell:next</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>IGNORE</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>cell:next</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>statement_number_label</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>cell:next</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>statement.number</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>cell:next</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>bill_to_label</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>cell:next</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>statement.bill_to</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>cell:next</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>date_label</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>cell:next</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>statement.date</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>cell:next</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>company_name_2_label</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>cell:next</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>IGNORE</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>cell:next</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>customer_id_label</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>cell:next</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>statement.customer_id</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>cell:next</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>street_address_2_label</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>cell:next</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>IGNORE</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>cell:next</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>address_2_label</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>cell:next</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>IGNORE</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>cell:next</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>city_state_zip_2_label</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>cell:next</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>IGNORE</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>table:*</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>HEADER:1</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>col_date</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>col_type</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>col_invoice</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>col_description</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>col_amount</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>col_payment</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>col_balance</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>DATA:9</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>line.date</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>line.type</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>line.invoice</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>line.description</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>line.amount</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>line.payment</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>line.balance</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>table:*</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>HEADER:1</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>col_customer_name</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>col_customer_value</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>DATA:5</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>remittance.customer_name</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>remittance.value</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
         <is>
           <t>END:</t>
         </is>

--- a/tests/fixtures/18_billing_statement/pattern.xlsx
+++ b/tests/fixtures/18_billing_statement/pattern.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I29"/>
+  <dimension ref="A1:I30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,7 +441,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>l_stmt</t>
+          <t>col_date</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -451,7 +451,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Statement #:</t>
+          <t>Date</t>
         </is>
       </c>
     </row>
@@ -463,7 +463,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>l_date</t>
+          <t>col_type</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -473,7 +473,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Date:</t>
+          <t>Type</t>
         </is>
       </c>
     </row>
@@ -485,7 +485,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>l_cust</t>
+          <t>col_invoice</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -495,7 +495,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Customer:</t>
+          <t>Invoice #</t>
         </is>
       </c>
     </row>
@@ -507,7 +507,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>c_date</t>
+          <t>col_description</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -517,7 +517,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Date</t>
+          <t>Description</t>
         </is>
       </c>
     </row>
@@ -529,7 +529,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>c_type</t>
+          <t>col_amount</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -539,7 +539,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Type</t>
+          <t>Amount</t>
         </is>
       </c>
     </row>
@@ -551,7 +551,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>c_inv</t>
+          <t>col_payment</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -561,7 +561,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Invoice #</t>
+          <t>Payment</t>
         </is>
       </c>
     </row>
@@ -573,7 +573,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>c_desc</t>
+          <t>col_balance</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -583,19 +583,19 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>Balance</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>lbl:</t>
+          <t>var:</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>c_amt</t>
+          <t>stmt.number</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -605,41 +605,41 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Amount</t>
+          <t>.*</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>lbl:</t>
+          <t>var:</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>c_pay</t>
+          <t>stmt.date</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>date</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Payment</t>
+          <t>.*</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>lbl:</t>
+          <t>var:</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>c_bal</t>
+          <t>stmt.customer_id</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Balance</t>
+          <t>.*</t>
         </is>
       </c>
     </row>
@@ -661,7 +661,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>statement.number</t>
+          <t>stmt.bill_to_name</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -671,7 +671,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>ST-\d+</t>
+          <t>.*</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>statement.date</t>
+          <t>line.date</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -701,7 +701,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>statement.customer</t>
+          <t>line.type</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -711,7 +711,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>.+</t>
+          <t>.*</t>
         </is>
       </c>
     </row>
@@ -723,15 +723,19 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>txn.date</t>
+          <t>line.invoice</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>\d+</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -741,7 +745,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>txn.type</t>
+          <t>line.description</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -751,7 +755,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>.+</t>
+          <t>.*</t>
         </is>
       </c>
     </row>
@@ -763,17 +767,17 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>txn.invoice</t>
+          <t>line.amount</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>currency</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>\d+</t>
+          <t>.*</t>
         </is>
       </c>
     </row>
@@ -785,17 +789,17 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>txn.description</t>
+          <t>line.payment</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>currency</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>.+</t>
+          <t>.*</t>
         </is>
       </c>
     </row>
@@ -807,7 +811,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>txn.amount</t>
+          <t>line.balance</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -829,7 +833,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>txn.payment</t>
+          <t>remittance.amount_due</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -846,65 +850,55 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>var:</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>txn.balance</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>currency</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>.*</t>
+          <t>START:</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>START:</t>
+          <t>cell:C8</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>stmt.number</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>cell:C7</t>
+          <t>cell:F8</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>statement.number</t>
+          <t>stmt.bill_to_name</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>cell:C8</t>
+          <t>cell:C9</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>statement.date</t>
+          <t>stmt.date</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>cell:C9</t>
+          <t>cell:C10</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>statement.customer</t>
+          <t>stmt.customer_id</t>
         </is>
       </c>
     </row>
@@ -923,37 +917,37 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>c_date</t>
+          <t>col_date</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>c_type</t>
+          <t>col_type</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>c_inv</t>
+          <t>col_invoice</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>c_desc</t>
+          <t>col_description</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>c_amt</t>
+          <t>col_amount</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>c_pay</t>
+          <t>col_payment</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>c_bal</t>
+          <t>col_balance</t>
         </is>
       </c>
     </row>
@@ -965,42 +959,54 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>txn.date</t>
+          <t>line.date</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>txn.type</t>
+          <t>line.type</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>txn.invoice</t>
+          <t>line.invoice</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>txn.description</t>
+          <t>line.description</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>txn.amount</t>
+          <t>line.amount</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>txn.payment</t>
+          <t>line.payment</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>txn.balance</t>
+          <t>line.balance</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
+        <is>
+          <t>cell:C30</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>remittance.amount_due</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
         <is>
           <t>END:</t>
         </is>
